--- a/data/CdS3_1/CdS3_1_Results Table.xlsx
+++ b/data/CdS3_1/CdS3_1_Results Table.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbdd27f2520478cf/Ambiente de Trabalho/TESE/Data_Analysis/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbdd27f2520478cf/Ambiente de Trabalho/TESE/Data_Analysis/data/CdS3_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2" documentId="8_{9164E8C4-4F24-4C48-82C3-D3E1711E5E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F91A6524-4C7E-47A2-A525-F32FC110A7B7}"/>
@@ -697,6 +697,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
